--- a/evaluations/classification/classification_results.xlsx
+++ b/evaluations/classification/classification_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,45 +456,50 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Use GV</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Alpha (fv sim - gv)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Geom. Candidates</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Min Inliers</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Inlier Threshold</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MAX GMM Descriptors</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Multiscale Enabled</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Run Time (minutes)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Top-5 Accuracy</t>
         </is>
@@ -512,7 +517,7 @@
         </is>
       </c>
       <c r="C2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
@@ -520,32 +525,35 @@
       <c r="E2" t="n">
         <v>96</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.35</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>20</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.5</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>1600000</v>
       </c>
-      <c r="K2" t="b">
+      <c r="L2" t="b">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>6.87</v>
-      </c>
       <c r="M2" t="n">
-        <v>0.7087</v>
+        <v>7.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8008</v>
+        <v>0.7818000000000001</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.8651</v>
       </c>
     </row>
   </sheetData>

--- a/evaluations/classification/classification_results.xlsx
+++ b/evaluations/classification/classification_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,72 +436,87 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Training Examples</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Num Classes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Remove Background</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>GMM Components</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PCA Components</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Use GV</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Alpha (fv sim - gv)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Geom. Candidates</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Min Inliers</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Inlier Threshold</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAX GMM Descriptors</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Multiscale Enabled</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Run Time (minutes)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Top-5 Accuracy</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>F-1 Score</t>
         </is>
       </c>
     </row>
@@ -511,49 +526,538 @@
           <t>ATRW</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C2" t="n">
+        <v>174</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>disk</t>
         </is>
       </c>
-      <c r="C2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>96</v>
       </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.35</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>20</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>10</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.5</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>1600000</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.7818000000000001</v>
+      <c r="N2" t="b">
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8651</v>
+        <v>7.03</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.7793</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8575</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.7613</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BelugaID</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6909</v>
+      </c>
+      <c r="C3" t="n">
+        <v>747</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>96</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0201</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CowDataset</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1019</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>96</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5958</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>906</v>
+      </c>
+      <c r="C5" t="n">
+        <v>170</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>96</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0245</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HyenaID2022</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2497</v>
+      </c>
+      <c r="C6" t="n">
+        <v>247</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>96</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2755</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5499</v>
+      </c>
+      <c r="C7" t="n">
+        <v>48</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>96</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.5056</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.7062</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5011</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C8" t="n">
+        <v>227</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>96</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1474</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0276</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1668</v>
+      </c>
+      <c r="C9" t="n">
+        <v>55</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>96</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.6777</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4477</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>655</v>
+      </c>
+      <c r="C10" t="n">
+        <v>43</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>96</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.8348</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.8290999999999999</v>
       </c>
     </row>
   </sheetData>
